--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,800 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1108,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,17 +1169,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1185,13 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1363,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1474,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1585,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1696,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1861,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1961,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1976,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2076,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2091,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2263,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2307,13 +2355,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2423,12 +2475,817 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>2/11</t>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1822,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1855,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,17 +1883,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1899,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1937,32 +1941,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1970,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1994,17 +2002,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2014,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2085,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2109,17 +2121,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2129,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2311,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2426,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2465,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2541,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,7 +2592,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2656,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2771,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2886,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3001,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3116,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3160,17 +3172,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3178,22 +3190,22 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3226,12 +3238,12 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3245,45 +3257,501 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>09:18</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="AC24" s="2" t="inlineStr">
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>4/11</t>
         </is>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2290,32 +2290,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2347,17 +2351,17 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2367,12 +2371,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2405,32 +2409,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2438,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2462,17 +2470,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2482,12 +2490,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2520,32 +2528,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2553,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2577,17 +2589,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2597,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2750,32 +2762,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2783,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2807,17 +2823,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2827,12 +2843,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2898,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2937,7 +2953,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2952,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3052,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3128,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3182,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3354,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3408,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3513,12 +3529,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3584,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3628,12 +3644,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3646,22 +3662,22 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3694,12 +3710,12 @@
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3713,47 +3729,392 @@
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr">
         <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>10:14</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr">
-        <is>
-          <t>4/11</t>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,14 +1541,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,18 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2370,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2608,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2619,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2784,12 +2788,12 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2799,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,14 +2842,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -2853,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2881,32 +2885,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2914,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2938,17 +2946,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2958,17 +2966,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2996,32 +3004,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3029,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3053,17 +3065,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3073,17 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3111,32 +3123,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3144,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3168,17 +3184,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3188,7 +3204,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3198,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3226,32 +3242,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -3259,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3283,33 +3303,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3337,32 +3361,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3370,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3394,37 +3422,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3539,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3567,32 +3595,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3600,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3624,37 +3656,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3769,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3869,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3884,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3989,17 +4021,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4104,17 +4136,592 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,22 +2489,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3480,32 +3480,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,37 +3541,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3605,24 +3609,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3632,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3681,12 +3685,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3714,32 +3718,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3747,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3771,17 +3779,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3791,12 +3799,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3862,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3944,32 +3952,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3977,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,17 +4013,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4021,17 +4033,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4059,32 +4071,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4092,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4116,37 +4132,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4322,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4376,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4410,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4437,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4451,7 +4467,7 @@
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4486,12 +4502,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4606,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4725,6 +4741,466 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,22 +2842,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4190,32 +4190,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4223,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,17 +4251,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4267,17 +4271,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4305,32 +4309,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -4338,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4362,17 +4370,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4382,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4420,32 +4428,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4453,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4477,17 +4489,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4497,12 +4509,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4535,32 +4547,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4568,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4592,37 +4608,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4737,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4880,32 +4896,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4913,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4937,17 +4957,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4957,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5143,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5187,17 +5207,477 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,17 +2489,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,17 +3556,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4438,24 +4438,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4781,32 +4781,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4814,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4838,17 +4842,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4858,12 +4862,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4906,24 +4910,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4933,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,12 +4986,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5015,32 +5019,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5048,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5072,32 +5080,32 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5130,32 +5138,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -5163,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5187,17 +5199,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5207,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,7 +5329,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5332,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5508,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5562,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,17 +5679,477 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr">
-        <is>
-          <t>6/11</t>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,17 +2842,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,17 +4623,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5029,24 +5029,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5257,32 +5257,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5290,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5314,17 +5318,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5334,17 +5338,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5372,32 +5376,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5405,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5429,32 +5437,32 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5487,32 +5495,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5520,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5544,37 +5556,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5602,32 +5614,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5635,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5659,17 +5675,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5679,17 +5695,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5789,7 +5805,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5804,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5914,7 +5930,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5980,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6095,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6139,17 +6155,477 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>3/11</t>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,22 +2608,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,22 +3199,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5624,24 +5624,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,22 +5690,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5733,32 +5733,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5766,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5790,17 +5794,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5810,12 +5814,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5848,32 +5852,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5881,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5905,17 +5913,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5925,17 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5963,32 +5971,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -5996,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6020,37 +6032,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6078,32 +6090,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6111,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,17 +6151,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6155,12 +6171,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6226,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6265,7 +6281,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6280,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6390,12 +6406,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6510,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6615,17 +6631,477 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>9/11</t>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,17 +4628,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5457,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5981,24 +5981,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6209,32 +6209,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6242,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6266,17 +6270,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6286,17 +6290,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6472,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6587,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6702,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6817,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6866,12 +6870,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6994,22 +6998,22 @@
       <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7047,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7061,47 +7065,162 @@
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr">
         <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>72.6</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
           <t>16:18</t>
         </is>
       </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W56" s="2" t="inlineStr">
+      <c r="W57" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X56" s="2" t="inlineStr">
+      <c r="X57" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y56" s="2" t="inlineStr">
+      <c r="Y57" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z56" s="2" t="inlineStr">
+      <c r="Z57" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr">
-        <is>
-          <t>75.5</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>10/11</t>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,22 +3080,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,22 +3199,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,22 +5333,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,22 +5690,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5814,17 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6100,24 +6100,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,22 +6166,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6219,24 +6219,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6328,32 +6328,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6361,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6385,32 +6389,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6443,32 +6447,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6476,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6500,37 +6508,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6558,32 +6566,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6591,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6615,17 +6627,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6635,17 +6647,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6673,32 +6685,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6706,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6730,37 +6746,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6875,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6975,7 +6991,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6990,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7166,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7215,12 +7231,702 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
           <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>71.4</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>72.4</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,22 +2489,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,22 +2608,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,17 +4628,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5457,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6290,17 +6290,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6804,32 +6804,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -6837,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,37 +6865,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6919,32 +6923,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -6952,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6976,17 +6984,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6996,17 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7034,32 +7042,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7067,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7091,37 +7103,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7149,32 +7161,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7182,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7206,17 +7222,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7226,17 +7242,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7336,7 +7352,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7412,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7466,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7642,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7757,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7811,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7916,17 +7932,592 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,17 +2723,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,22 +3318,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,17 +3437,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,17 +3794,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,17 +4028,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,22 +4385,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,17 +4976,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,22 +5214,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,17 +5333,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,22 +5571,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5695,17 +5695,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,17 +5809,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,17 +6166,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6404,22 +6404,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6523,17 +6523,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6642,17 +6642,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6766,17 +6766,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,22 +6999,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7052,24 +7052,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7183,12 +7183,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7280,32 +7280,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7313,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7337,32 +7341,32 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7395,32 +7399,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7428,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,37 +7460,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7510,32 +7518,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7543,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7567,32 +7579,32 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7625,32 +7637,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7658,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7682,32 +7698,32 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7740,32 +7756,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7773,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7797,17 +7817,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7817,17 +7837,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7855,32 +7875,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -7888,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7912,37 +7936,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7970,32 +7994,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8003,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8027,32 +8055,32 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8118,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8167,12 +8195,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8272,7 +8300,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8348,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8387,17 +8415,17 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8410,22 +8438,22 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8458,12 +8486,12 @@
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8477,47 +8505,852 @@
       <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr">
         <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>74.4</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="V68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr">
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y68" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z68" s="2" t="inlineStr">
+      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
+      <c r="AA69" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
+      <c r="AB69" s="2" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AC68" s="2" t="inlineStr">
+      <c r="AC69" s="2" t="inlineStr">
         <is>
           <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,22 +2608,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,17 +4976,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,22 +5571,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6404,22 +6404,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6523,17 +6523,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,22 +6880,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7123,17 +7123,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7361,17 +7361,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,22 +7475,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,17 +7594,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7885,24 +7885,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -8113,32 +8113,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8146,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8170,17 +8174,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8190,17 +8194,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -8228,32 +8232,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8261,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8285,17 +8293,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8305,12 +8313,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8343,32 +8351,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8376,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8400,17 +8412,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8420,17 +8432,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -8458,32 +8470,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8491,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8515,37 +8531,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -8573,32 +8589,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -8606,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8630,37 +8650,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8688,32 +8708,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8721,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8745,17 +8769,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8765,12 +8789,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8803,32 +8827,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8836,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8860,32 +8888,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8951,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9000,12 +9028,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9105,7 +9133,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9115,12 +9143,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9225,12 +9253,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9296,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9340,17 +9368,477 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>71.4</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC79"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7004,17 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,22 +7356,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7956,17 +7956,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8313,17 +8313,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8427,22 +8427,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8718,24 +8718,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8837,24 +8837,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8979,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,17 +9007,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9023,12 +9027,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9061,32 +9065,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -9094,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9118,17 +9126,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9138,17 +9146,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -9176,32 +9184,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9209,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9233,17 +9245,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9253,17 +9265,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -9291,32 +9303,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9324,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9348,37 +9364,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9554,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9593,7 +9609,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9608,7 +9624,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9718,12 +9734,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,17 +9844,247 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>73.6</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr">
-        <is>
-          <t>5/11</t>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5576,17 +5576,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6052,17 +6052,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6409,17 +6409,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7480,17 +7480,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8551,17 +8551,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9146,12 +9146,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -9422,32 +9422,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9455,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,17 +9483,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9499,17 +9503,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9537,32 +9541,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9570,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9594,17 +9602,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9614,17 +9622,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9652,32 +9660,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9685,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9709,17 +9721,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9729,12 +9741,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9767,32 +9779,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -9800,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9824,17 +9840,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9844,12 +9860,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9915,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9969,7 +9985,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10074,17 +10090,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-182路.xlsx
+++ b/data/export/2026-10-11-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9789,24 +9789,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9898,32 +9898,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9931,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,17 +9959,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9975,12 +9979,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10013,32 +10017,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10046,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10070,17 +10078,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10090,12 +10098,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
